--- a/rmonize/data_dictionary/DD_NAKO_P2.xlsx
+++ b/rmonize/data_dictionary/DD_NAKO_P2.xlsx
@@ -383,7 +383,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>age_anth_fup</t>
+          <t>basis_age_fup</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">

--- a/rmonize/data_dictionary/DD_NAKO_P2.xlsx
+++ b/rmonize/data_dictionary/DD_NAKO_P2.xlsx
@@ -743,7 +743,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>anthro_bmi</t>
+          <t>anthro_BMI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>gcal</t>
+          <t>a_nu_gcal</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">

--- a/rmonize/data_dictionary/DD_NAKO_P2.xlsx
+++ b/rmonize/data_dictionary/DD_NAKO_P2.xlsx
@@ -1404,7 +1404,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1423,6 +1423,11 @@
           <t>label</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1438,6 +1443,11 @@
           <t>Mannlich</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1453,19 +1463,29 @@
           <t>Weiblich</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>a_ses_isced11_level</t>
+          <t>basis_sex</t>
         </is>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Less than primary education (Not applicable for Germany)</t>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -1476,11 +1496,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Primary education</t>
+          <t>Less than primary education (Not applicable for Germany)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -1491,11 +1516,16 @@
         </is>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lower secondary education</t>
+          <t>Primary education</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -1506,11 +1536,16 @@
         </is>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Upper secondary education</t>
+          <t>Lower secondary education</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -1521,11 +1556,16 @@
         </is>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Post-secondary non-tertiary education</t>
+          <t>Upper secondary education</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -1536,11 +1576,16 @@
         </is>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Short-cycle tertiary education (Not applicable for Germany)</t>
+          <t>Post-secondary non-tertiary education</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -1551,11 +1596,16 @@
         </is>
       </c>
       <c r="B10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bachelor's or equivalent level</t>
+          <t>Short-cycle tertiary education (Not applicable for Germany)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -1566,11 +1616,16 @@
         </is>
       </c>
       <c r="B11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Master's or equivalent level</t>
+          <t>Bachelor's or equivalent level</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -1581,108 +1636,143 @@
         </is>
       </c>
       <c r="B12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Doctoral or equivalent level</t>
+          <t>Master's or equivalent level</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>a_smok_stat_qn</t>
+          <t>a_ses_isced11_level</t>
         </is>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kein Raucher, auch nicht ehemalig</t>
+          <t>Doctoral or equivalent level</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>a_smok_stat_qn</t>
+          <t>a_ses_isced11_level</t>
         </is>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ehemaliger Raucher</t>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>a_smok_stat_qn</t>
+          <t>a_ses_isced11_level</t>
         </is>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>-9</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Raucher</t>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>a_smok_stat_qn</t>
+          <t>a_ses_isced11_level</t>
         </is>
       </c>
       <c r="B16">
-        <v>4</v>
+        <v>-88</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rauchstatus unbekannt</t>
+          <t>still in general-education school training and without a vocational qualification</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>a_diab</t>
+          <t>a_ses_isced11_level</t>
         </is>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>-99</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>still in vocational training</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>a_diab</t>
+          <t>a_gpaq_ptotalmet</t>
         </is>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>777777</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>d_f_mp1</t>
+          <t>a_smok_stat_qn</t>
         </is>
       </c>
       <c r="B19">
@@ -1690,14 +1780,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Kein Raucher, auch nicht ehemalig</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>d_f_mp1</t>
+          <t>a_smok_stat_qn</t>
         </is>
       </c>
       <c r="B20">
@@ -1705,67 +1800,1312 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Ehemaliger Raucher</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>d_an_ca</t>
+          <t>a_smok_stat_qn</t>
         </is>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Raucher</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>d_an_ca</t>
+          <t>a_smok_stat_qn</t>
         </is>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Rauchstatus unbekannt</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>d_an_cv_6</t>
+          <t>a_packyears</t>
         </is>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>7777</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>missing due to impossible calculation</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>a_packyears</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>8886</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Implausible information</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>a_packyears</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>7776</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Calculation not possible due to implausible values</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>a_packyears</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>7775</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Allowed skipped</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>a_packyears</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>8888</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>a_packyears</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>9999</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Don't know</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>a_packyears</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>8889</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Not specified, erroneously skipped</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>d_sn1</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>9999</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>I don't know</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>d_sn1</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>8888</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>no answer</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>d_sn1</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>7777</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>implausible</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>d_f_mp1</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>d_f_mp1</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>2</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>d_f_mp1</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>9999</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>I don't know</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>d_f_mp1</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>8888</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>no answer</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>d_an_ca</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>d_an_ca</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>2</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>d_an_ca</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>9999</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>I don't know</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>d_an_ca</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>8888</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>no answer</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>a_diab</t>
+        </is>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>a_diab</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>a_diab</t>
+        </is>
+      </c>
+      <c r="B43">
+        <v>9</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>d_an_cv_6</t>
         </is>
       </c>
-      <c r="B24">
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>d_an_cv_6</t>
+        </is>
+      </c>
+      <c r="B45">
         <v>2</v>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Nein</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>d_an_cv_6</t>
+        </is>
+      </c>
+      <c r="B46">
+        <v>9999</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>I don't know</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>d_an_cv_6</t>
+        </is>
+      </c>
+      <c r="B47">
+        <v>8888</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>no answer</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>sa_trig</t>
+        </is>
+      </c>
+      <c r="B48">
+        <v>111111</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Sample too old</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>sa_trig</t>
+        </is>
+      </c>
+      <c r="B49">
+        <v>222222</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Hemolytic sample</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>sa_trig</t>
+        </is>
+      </c>
+      <c r="B50">
+        <v>333333</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>lipemic sample</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>sa_trig</t>
+        </is>
+      </c>
+      <c r="B51">
+        <v>444444</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Technically not possible</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>sa_trig</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>555555</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Planned not determined</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>sa_trig</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>999999</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>no valid information available</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>sa_chol</t>
+        </is>
+      </c>
+      <c r="B54">
+        <v>111111</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Sample too old</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>sa_chol</t>
+        </is>
+      </c>
+      <c r="B55">
+        <v>222222</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Hemolytic sample</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>sa_chol</t>
+        </is>
+      </c>
+      <c r="B56">
+        <v>333333</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>lipemic sample</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>sa_chol</t>
+        </is>
+      </c>
+      <c r="B57">
+        <v>444444</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Technically not possible</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>sa_chol</t>
+        </is>
+      </c>
+      <c r="B58">
+        <v>555555</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Planned not determined</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>sa_chol</t>
+        </is>
+      </c>
+      <c r="B59">
+        <v>999999</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>no valid information available</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>sa_chol</t>
+        </is>
+      </c>
+      <c r="B60">
+        <v>666666</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Eliminated by group of experts</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>sa_ldlc</t>
+        </is>
+      </c>
+      <c r="B61">
+        <v>111111</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Sample too old</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>sa_ldlc</t>
+        </is>
+      </c>
+      <c r="B62">
+        <v>222222</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Hemolytic sample</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>sa_ldlc</t>
+        </is>
+      </c>
+      <c r="B63">
+        <v>333333</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>lipemic sample</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>sa_ldlc</t>
+        </is>
+      </c>
+      <c r="B64">
+        <v>444444</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Technically not possible</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>sa_ldlc</t>
+        </is>
+      </c>
+      <c r="B65">
+        <v>555555</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Planned not determined</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>sa_ldlc</t>
+        </is>
+      </c>
+      <c r="B66">
+        <v>999999</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>no valid information available</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>sa_ldlc</t>
+        </is>
+      </c>
+      <c r="B67">
+        <v>666666</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Eliminated by group of experts</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>a_anthro_bmi</t>
+        </is>
+      </c>
+      <c r="B68">
+        <v>7777</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>missing due to impossible calculation</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>a_anthro_bmi</t>
+        </is>
+      </c>
+      <c r="B69">
+        <v>8886</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Implausible information</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>a_anthro_bmi</t>
+        </is>
+      </c>
+      <c r="B70">
+        <v>7776</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Calculation not possible due to implausible values</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>a_anthro_bmi</t>
+        </is>
+      </c>
+      <c r="B71">
+        <v>7775</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Allowed skipped</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>a_anthro_bmi</t>
+        </is>
+      </c>
+      <c r="B72">
+        <v>8888</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>a_anthro_bmi</t>
+        </is>
+      </c>
+      <c r="B73">
+        <v>9999</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Don't know</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>a_anthro_bmi</t>
+        </is>
+      </c>
+      <c r="B74">
+        <v>8889</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Not specified, erroneously skipped</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>a_anthro_fettmasse</t>
+        </is>
+      </c>
+      <c r="B75">
+        <v>7777</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>missing data</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>a_anthro_fettmasse</t>
+        </is>
+      </c>
+      <c r="B76">
+        <v>8886</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Implausible information</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>a_anthro_fettmasse</t>
+        </is>
+      </c>
+      <c r="B77">
+        <v>7776</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>calculation not possible due to implausible</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>a_anthro_fettmasse</t>
+        </is>
+      </c>
+      <c r="B78">
+        <v>7775</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Allowed skipped</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>a_anthro_fettmasse</t>
+        </is>
+      </c>
+      <c r="B79">
+        <v>8888</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>a_anthro_fettmasse</t>
+        </is>
+      </c>
+      <c r="B80">
+        <v>9999</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Don't know</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>a_anthro_fettmasse</t>
+        </is>
+      </c>
+      <c r="B81">
+        <v>8889</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Not specified, erroneously skipped</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>anthro_taillenumfang</t>
+        </is>
+      </c>
+      <c r="B82">
+        <v>9999</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>anthro_taillenumfang_fup</t>
+        </is>
+      </c>
+      <c r="B83">
+        <v>9999</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>anthro_hueftumfang</t>
+        </is>
+      </c>
+      <c r="B84">
+        <v>9999</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>anthro_hueftumfang_fup</t>
+        </is>
+      </c>
+      <c r="B85">
+        <v>9999</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
